--- a/artfynd/A 33733-2020 artfynd.xlsx
+++ b/artfynd/A 33733-2020 artfynd.xlsx
@@ -743,6 +743,11 @@
           <t>Degeberga</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>M-Kri-2466</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
           <t>2003-07-08</t>

--- a/artfynd/A 33733-2020 artfynd.xlsx
+++ b/artfynd/A 33733-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122118605</v>
       </c>
       <c r="B2" t="n">
-        <v>110020</v>
+        <v>110029</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 33733-2020 artfynd.xlsx
+++ b/artfynd/A 33733-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122118605</v>
       </c>
       <c r="B2" t="n">
-        <v>110055</v>
+        <v>110065</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 33733-2020 artfynd.xlsx
+++ b/artfynd/A 33733-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122118605</v>
       </c>
       <c r="B2" t="n">
-        <v>110065</v>
+        <v>110078</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 33733-2020 artfynd.xlsx
+++ b/artfynd/A 33733-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122118605</v>
       </c>
       <c r="B2" t="n">
-        <v>110078</v>
+        <v>110083</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 33733-2020 artfynd.xlsx
+++ b/artfynd/A 33733-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122118605</v>
       </c>
       <c r="B2" t="n">
-        <v>110083</v>
+        <v>110092</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>221049</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Småvänderot</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 33733-2020 artfynd.xlsx
+++ b/artfynd/A 33733-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122118605</v>
       </c>
       <c r="B2" t="n">
-        <v>110092</v>
+        <v>110105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>221049</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Småvänderot</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
